--- a/other/background_information_sheet_form.xlsx
+++ b/other/background_information_sheet_form.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1075,7 +1075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -1239,34 +1239,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_details_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_choices</t>
+          <t>emergency_contact_details_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sister</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -1329,46 +1329,46 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>sister</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Sister</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_status_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>mother</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Mother</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>emergency_contact_relationship_status_choices</t>
+          <t>emergency_contact_relationship_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>father</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>brother</t>
+          <t>mother</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brother</t>
+          <t>Mother</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sister</t>
+          <t>father</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sister</t>
+          <t>Father</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>spouse</t>
+          <t>brother</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spouse</t>
+          <t>Brother</t>
         </is>
       </c>
     </row>
@@ -1431,10 +1431,44 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
+          <t>sister</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sister</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>emergency_contact_relationship_status_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>spouse</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Spouse</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>emergency_contact_relationship_status_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>other</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
